--- a/2025全年训练日期汇总.xlsx
+++ b/2025全年训练日期汇总.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aresp\Desktop\usercode\TrainingRecord\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C8FED-31BA-401B-BF1D-D6A57DC833C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="10455" activeTab="2"/>
+    <workbookView xWindow="38805" yWindow="4200" windowWidth="23550" windowHeight="16665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封面" sheetId="1" r:id="rId1"/>
@@ -34,12 +40,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="281">
   <si>
     <t>月份</t>
   </si>
@@ -561,9 +570,6 @@
   </si>
   <si>
     <t>2025-08-22</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
   </si>
   <si>
     <t>9月训练日期</t>
@@ -890,14 +896,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -912,352 +915,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1265,313 +938,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1856,22 +1244,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.75221238938053" customWidth="1"/>
-    <col min="2" max="3" width="16.3716814159292" customWidth="1"/>
-    <col min="4" max="5" width="21.3716814159292" customWidth="1"/>
-    <col min="6" max="6" width="7.75221238938053" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="5" width="21.375" customWidth="1"/>
+    <col min="6" max="6" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1891,7 +1279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1916,13 +1304,13 @@
         <v>11200</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
         <f>SUMIFS('2月'!C:C,'2月'!B:B,"否")</f>
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="C3">
         <f>SUMIFS('2月'!C:C,'2月'!B:B,"是")</f>
@@ -1930,7 +1318,7 @@
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>1450</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
@@ -1938,16 +1326,16 @@
       </c>
       <c r="F3">
         <f t="shared" si="2"/>
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <f>SUMIFS('3月'!C:C,'3月'!B:B,"否")</f>
-        <v>33</v>
+        <v>22.5</v>
       </c>
       <c r="C4">
         <f>SUMIFS('3月'!C:C,'3月'!B:B,"是")</f>
@@ -1955,7 +1343,7 @@
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>2250</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
@@ -1963,16 +1351,16 @@
       </c>
       <c r="F4">
         <f t="shared" si="2"/>
-        <v>11300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
         <f>SUMIFS('4月'!C:C,'4月'!B:B,"否")</f>
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <f>SUMIFS('4月'!C:C,'4月'!B:B,"是")</f>
@@ -1980,7 +1368,7 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
@@ -1988,10 +1376,10 @@
       </c>
       <c r="F5">
         <f t="shared" si="2"/>
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2016,7 +1404,7 @@
         <v>8450</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2041,7 +1429,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2066,7 +1454,7 @@
         <v>36800</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2076,7 +1464,7 @@
       </c>
       <c r="C9">
         <f>SUMIFS('8月'!C:C,'8月'!B:B,"是")</f>
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2084,14 +1472,14 @@
       </c>
       <c r="E9">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>25600</v>
       </c>
       <c r="F9">
         <f t="shared" si="2"/>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2116,7 +1504,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +1529,7 @@
         <v>13300</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2166,7 +1554,7 @@
         <v>10200</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2191,42 +1579,41 @@
         <v>8750</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B13)</f>
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="C14">
         <f>SUM(C2:C13)</f>
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="D14">
         <f>SUM(D2:D13)</f>
-        <v>20800</v>
+        <v>18100</v>
       </c>
       <c r="E14">
         <f>SUM(E2:E13)</f>
-        <v>131200</v>
+        <v>132800</v>
       </c>
       <c r="F14">
         <f>SUM(F2:F13)</f>
-        <v>152000</v>
+        <v>150900</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2234,9 +1621,9 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
@@ -2248,9 +1635,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
@@ -2263,54 +1650,54 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>177</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>178</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>179</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>180</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -2323,84 +1710,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>181</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>182</v>
       </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>183</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>184</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>185</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>186</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -2413,84 +1800,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>187</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <v>0.5</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>188</v>
       </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14">
-        <v>0.5</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>189</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>190</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>191</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>192</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -2503,84 +1890,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
         <v>193</v>
       </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>0.5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
         <v>194</v>
       </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20">
-        <v>0.5</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>195</v>
       </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21">
-        <v>0.5</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
         <v>196</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
         <v>197</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>198</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -2593,40 +1980,40 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
         <v>199</v>
       </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
         <v>200</v>
       </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26">
-        <v>0.5</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>201</v>
-      </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
@@ -2639,16 +2026,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2656,9 +2042,9 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
@@ -2670,9 +2056,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -2685,84 +2071,84 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>204</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>205</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>206</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>207</v>
       </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>208</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>209</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -2775,84 +2161,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>210</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>211</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>212</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>213</v>
       </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>0.5</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>0.5</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>215</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -2865,84 +2251,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>216</v>
       </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>217</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>218</v>
       </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>219</v>
       </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18">
-        <v>0.5</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
         <v>220</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19">
-        <v>0.5</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>221</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
@@ -2955,84 +2341,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>222</v>
       </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21">
-        <v>8</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
         <v>223</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
         <v>224</v>
       </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
         <v>225</v>
       </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>0.5</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
         <v>226</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25">
-        <v>0.5</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>227</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -3046,16 +2432,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -3063,9 +2448,9 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
@@ -3077,9 +2462,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -3092,69 +2477,69 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>230</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>231</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>232</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>233</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>234</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -3167,84 +2552,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>235</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>236</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>237</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>238</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>239</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>0.5</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>240</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -3257,84 +2642,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>241</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14">
-        <v>8</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>242</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>243</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>244</v>
       </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>245</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18">
-        <v>0.5</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>246</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -3347,84 +2732,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
         <v>247</v>
       </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20">
-        <v>8</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>248</v>
       </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21">
-        <v>0.5</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
         <v>249</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
         <v>250</v>
       </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
         <v>251</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>0.5</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>252</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -3437,9 +2822,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -3453,16 +2838,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -3470,9 +2854,9 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
@@ -3484,9 +2868,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
@@ -3499,54 +2883,54 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>256</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>257</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>258</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>259</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -3559,84 +2943,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>260</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>261</v>
       </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>262</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>263</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>264</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>265</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -3649,84 +3033,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>266</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <v>0.5</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>267</v>
       </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14">
-        <v>0.5</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>268</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>269</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>0.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>270</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>271</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -3739,84 +3123,84 @@
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
         <v>272</v>
       </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>0.5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
         <v>273</v>
       </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20">
-        <v>0.5</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>274</v>
       </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21">
-        <v>0.5</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
         <v>275</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
         <v>276</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>277</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -3829,55 +3213,55 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
+        <v>277</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
         <v>278</v>
       </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
         <v>279</v>
       </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26">
-        <v>0.5</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
         <v>280</v>
       </c>
-      <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27">
-        <v>0.5</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>281</v>
-      </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
@@ -3890,16 +3274,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -3907,7 +3290,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -3921,7 +3304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3936,7 +3319,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -3951,7 +3334,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -3966,7 +3349,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3981,7 +3364,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -3996,7 +3379,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -4011,7 +3394,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -4027,16 +3410,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -4044,7 +3426,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -4058,7 +3440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -4066,14 +3448,14 @@
         <v>33</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:D14" si="0">IF(B2="","",IF(B2="是",C2*200,IF(B2="否",C2*100,"")))</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -4088,7 +3470,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -4096,14 +3478,14 @@
         <v>33</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -4111,14 +3493,14 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -4126,14 +3508,14 @@
         <v>33</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -4141,14 +3523,14 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -4156,14 +3538,14 @@
         <v>33</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -4178,7 +3560,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4186,14 +3568,14 @@
         <v>33</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -4201,14 +3583,14 @@
         <v>33</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -4216,14 +3598,14 @@
         <v>33</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4231,14 +3613,14 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -4246,24 +3628,23 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -4271,7 +3652,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -4285,7 +3666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -4300,7 +3681,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -4308,14 +3689,14 @@
         <v>33</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -4323,14 +3704,14 @@
         <v>33</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -4338,14 +3719,14 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -4353,14 +3734,14 @@
         <v>33</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -4368,14 +3749,14 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -4390,7 +3771,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -4398,14 +3779,14 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -4413,14 +3794,14 @@
         <v>33</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -4428,14 +3809,14 @@
         <v>33</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -4443,14 +3824,14 @@
         <v>33</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -4458,14 +3839,14 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -4480,7 +3861,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -4488,14 +3869,14 @@
         <v>33</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -4503,14 +3884,14 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -4518,14 +3899,14 @@
         <v>33</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -4533,14 +3914,14 @@
         <v>33</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -4548,14 +3929,14 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -4570,7 +3951,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -4578,14 +3959,14 @@
         <v>33</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -4593,14 +3974,14 @@
         <v>33</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -4608,14 +3989,14 @@
         <v>33</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -4623,14 +4004,14 @@
         <v>33</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D24">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -4638,14 +4019,14 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -4660,7 +4041,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -4668,24 +4049,23 @@
         <v>33</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -4693,7 +4073,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -4707,7 +4087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -4715,14 +4095,14 @@
         <v>33</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:D27" si="0">IF(B2="","",IF(B2="是",C2*200,IF(B2="否",C2*100,"")))</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -4730,14 +4110,14 @@
         <v>33</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>76</v>
       </c>
@@ -4745,14 +4125,14 @@
         <v>33</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -4760,14 +4140,14 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -4782,7 +4162,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -4790,14 +4170,14 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -4805,14 +4185,14 @@
         <v>33</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -4820,14 +4200,14 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -4835,14 +4215,14 @@
         <v>33</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -4850,14 +4230,14 @@
         <v>33</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -4872,7 +4252,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -4880,14 +4260,14 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -4895,14 +4275,14 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -4910,14 +4290,14 @@
         <v>33</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -4925,14 +4305,14 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -4940,14 +4320,14 @@
         <v>33</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -4962,7 +4342,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -4970,14 +4350,14 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -4985,14 +4365,14 @@
         <v>33</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -5000,14 +4380,14 @@
         <v>33</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -5015,14 +4395,14 @@
         <v>33</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -5030,14 +4410,14 @@
         <v>33</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>96</v>
       </c>
@@ -5052,7 +4432,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -5060,14 +4440,14 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -5075,14 +4455,14 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>99</v>
       </c>
@@ -5090,24 +4470,23 @@
         <v>33</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5115,7 +4494,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -5129,7 +4508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -5144,7 +4523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -5159,7 +4538,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -5174,7 +4553,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -5189,7 +4568,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -5204,7 +4583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -5219,7 +4598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -5234,7 +4613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -5249,7 +4628,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>109</v>
       </c>
@@ -5264,7 +4643,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -5279,7 +4658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -5294,7 +4673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -5309,7 +4688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -5324,7 +4703,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -5339,7 +4718,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -5354,7 +4733,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -5369,7 +4748,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>117</v>
       </c>
@@ -5384,7 +4763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -5399,7 +4778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>119</v>
       </c>
@@ -5414,7 +4793,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -5429,7 +4808,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>121</v>
       </c>
@@ -5445,16 +4824,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5462,7 +4840,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
@@ -5476,7 +4854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -5491,7 +4869,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -5506,7 +4884,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -5521,7 +4899,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -5536,7 +4914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>127</v>
       </c>
@@ -5551,7 +4929,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -5566,7 +4944,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>129</v>
       </c>
@@ -5581,7 +4959,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -5596,7 +4974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>131</v>
       </c>
@@ -5611,7 +4989,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -5626,7 +5004,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>133</v>
       </c>
@@ -5641,7 +5019,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>134</v>
       </c>
@@ -5657,16 +5035,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5674,7 +5051,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>135</v>
       </c>
@@ -5688,7 +5065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -5703,7 +5080,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -5718,7 +5095,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -5733,7 +5110,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>139</v>
       </c>
@@ -5748,7 +5125,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>140</v>
       </c>
@@ -5763,7 +5140,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -5778,7 +5155,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>142</v>
       </c>
@@ -5793,7 +5170,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -5808,7 +5185,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>144</v>
       </c>
@@ -5823,7 +5200,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>145</v>
       </c>
@@ -5838,7 +5215,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -5853,7 +5230,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>147</v>
       </c>
@@ -5868,7 +5245,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -5883,7 +5260,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>149</v>
       </c>
@@ -5898,7 +5275,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -5913,7 +5290,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -5928,7 +5305,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>152</v>
       </c>
@@ -5943,7 +5320,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>153</v>
       </c>
@@ -5958,7 +5335,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>154</v>
       </c>
@@ -5973,7 +5350,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -5988,7 +5365,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>156</v>
       </c>
@@ -6003,7 +5380,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -6018,7 +5395,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>158</v>
       </c>
@@ -6034,16 +5411,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -6051,7 +5427,7 @@
     <col min="4" max="4" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>159</v>
       </c>
@@ -6065,8 +5441,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B2" t="s">
@@ -6080,8 +5456,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="B3" t="s">
@@ -6095,8 +5471,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B4" t="s">
@@ -6110,8 +5486,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B5" t="s">
@@ -6125,8 +5501,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B6" t="s">
@@ -6140,8 +5516,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B7" t="s">
@@ -6155,8 +5531,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B8" t="s">
@@ -6170,8 +5546,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B9" t="s">
@@ -6185,8 +5561,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B10" t="s">
@@ -6200,8 +5576,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B11" t="s">
@@ -6215,8 +5591,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B12" t="s">
@@ -6230,8 +5606,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
         <v>171</v>
       </c>
       <c r="B13" t="s">
@@ -6245,8 +5621,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B14" t="s">
@@ -6260,8 +5636,8 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B15" t="s">
@@ -6275,9 +5651,9 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>174</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>45892</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -6290,8 +5666,23 @@
         <v>1600</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>45893</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17" si="1">IF(B17="","",IF(B17="是",C17*200,IF(B17="否",C17*100,"")))</f>
+        <v>1600</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>